--- a/dorim-redev-system/data/members.xlsx
+++ b/dorim-redev-system/data/members.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F21"/>
+  <dimension ref="A1:U21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -424,27 +424,102 @@
       </c>
       <c r="B1" t="inlineStr">
         <is>
+          <t>name</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>phone</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>birth_date</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
           <t>address</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
-        <is>
-          <t>birth_date</t>
-        </is>
-      </c>
-      <c r="D1" t="inlineStr">
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>current_address</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
+          <t>ownership_type</t>
+        </is>
+      </c>
+      <c r="H1" t="inlineStr">
+        <is>
+          <t>land_area</t>
+        </is>
+      </c>
+      <c r="I1" t="inlineStr">
+        <is>
+          <t>building_area</t>
+        </is>
+      </c>
+      <c r="J1" t="inlineStr">
+        <is>
+          <t>has_illegal_building</t>
+        </is>
+      </c>
+      <c r="K1" t="inlineStr">
+        <is>
+          <t>prev_asset_value</t>
+        </is>
+      </c>
+      <c r="L1" t="inlineStr">
+        <is>
+          <t>proportional_rate</t>
+        </is>
+      </c>
+      <c r="M1" t="inlineStr">
+        <is>
+          <t>rights_value</t>
+        </is>
+      </c>
+      <c r="N1" t="inlineStr">
         <is>
           <t>is_sale_target</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
-        <is>
-          <t>rights_value</t>
-        </is>
-      </c>
-      <c r="F1" t="inlineStr">
+      <c r="O1" t="inlineStr">
+        <is>
+          <t>alloc_area_type</t>
+        </is>
+      </c>
+      <c r="P1" t="inlineStr">
+        <is>
+          <t>estimated_alloc_price</t>
+        </is>
+      </c>
+      <c r="Q1" t="inlineStr">
+        <is>
+          <t>relocation_cost</t>
+        </is>
+      </c>
+      <c r="R1" t="inlineStr">
+        <is>
+          <t>settlement_amount</t>
+        </is>
+      </c>
+      <c r="S1" t="inlineStr">
         <is>
           <t>consent</t>
+        </is>
+      </c>
+      <c r="T1" t="inlineStr">
+        <is>
+          <t>consent_date</t>
+        </is>
+      </c>
+      <c r="U1" t="inlineStr">
+        <is>
+          <t>memo</t>
         </is>
       </c>
     </row>
@@ -454,23 +529,78 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
+          <t>김도림</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>010-1000-5000</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>1955-03-15</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
           <t>서울 영등포구 도림동 239-12</t>
         </is>
       </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>1955-03-15</t>
-        </is>
-      </c>
-      <c r="D2" t="b">
-        <v>1</v>
-      </c>
-      <c r="E2" t="n">
-        <v>185000000</v>
-      </c>
-      <c r="F2" t="b">
-        <v>1</v>
-      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>서울 영등포구 도림동 239-12</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>토지+건물</t>
+        </is>
+      </c>
+      <c r="H2" t="n">
+        <v>45.2</v>
+      </c>
+      <c r="I2" t="n">
+        <v>82.5</v>
+      </c>
+      <c r="J2" t="b">
+        <v>0</v>
+      </c>
+      <c r="K2" t="n">
+        <v>180000000</v>
+      </c>
+      <c r="L2" t="n">
+        <v>110</v>
+      </c>
+      <c r="M2" t="n">
+        <v>198000000</v>
+      </c>
+      <c r="N2" t="b">
+        <v>1</v>
+      </c>
+      <c r="O2" t="inlineStr">
+        <is>
+          <t>84A</t>
+        </is>
+      </c>
+      <c r="P2" t="n">
+        <v>540000000</v>
+      </c>
+      <c r="Q2" t="n">
+        <v>118800000</v>
+      </c>
+      <c r="R2" t="n">
+        <v>342000000</v>
+      </c>
+      <c r="S2" t="b">
+        <v>1</v>
+      </c>
+      <c r="T2" t="inlineStr">
+        <is>
+          <t>2024-03-20</t>
+        </is>
+      </c>
+      <c r="U2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -478,23 +608,78 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
+          <t>이영등</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>010-1001-5001</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>1962-07-22</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
           <t>서울 영등포구 도림동 239-14</t>
         </is>
       </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>1962-07-22</t>
-        </is>
-      </c>
-      <c r="D3" t="b">
-        <v>1</v>
-      </c>
-      <c r="E3" t="n">
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>서울 영등포구 도림동 239-14</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>토지+건물</t>
+        </is>
+      </c>
+      <c r="H3" t="n">
+        <v>62</v>
+      </c>
+      <c r="I3" t="n">
+        <v>115.3</v>
+      </c>
+      <c r="J3" t="b">
+        <v>0</v>
+      </c>
+      <c r="K3" t="n">
         <v>220000000</v>
       </c>
-      <c r="F3" t="b">
-        <v>1</v>
-      </c>
+      <c r="L3" t="n">
+        <v>110</v>
+      </c>
+      <c r="M3" t="n">
+        <v>242000000</v>
+      </c>
+      <c r="N3" t="b">
+        <v>1</v>
+      </c>
+      <c r="O3" t="inlineStr">
+        <is>
+          <t>84A</t>
+        </is>
+      </c>
+      <c r="P3" t="n">
+        <v>640000000</v>
+      </c>
+      <c r="Q3" t="n">
+        <v>145200000</v>
+      </c>
+      <c r="R3" t="n">
+        <v>398000000</v>
+      </c>
+      <c r="S3" t="b">
+        <v>1</v>
+      </c>
+      <c r="T3" t="inlineStr">
+        <is>
+          <t>2024-04-05</t>
+        </is>
+      </c>
+      <c r="U3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -502,22 +687,77 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
+          <t>박서울</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>010-1002-5002</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>1948-11-08</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
           <t>서울 영등포구 도림동 239-16</t>
         </is>
       </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>1948-11-08</t>
-        </is>
-      </c>
-      <c r="D4" t="b">
-        <v>0</v>
-      </c>
-      <c r="E4" t="n">
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>서울 영등포구 도림동 239-16</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>토지만</t>
+        </is>
+      </c>
+      <c r="H4" t="n">
+        <v>38.5</v>
+      </c>
+      <c r="I4" t="n">
+        <v>68</v>
+      </c>
+      <c r="J4" t="b">
+        <v>0</v>
+      </c>
+      <c r="K4" t="n">
         <v>145000000</v>
       </c>
-      <c r="F4" t="b">
-        <v>0</v>
+      <c r="L4" t="n">
+        <v>110</v>
+      </c>
+      <c r="M4" t="n">
+        <v>159500000</v>
+      </c>
+      <c r="N4" t="b">
+        <v>1</v>
+      </c>
+      <c r="O4" t="inlineStr">
+        <is>
+          <t>59A</t>
+        </is>
+      </c>
+      <c r="P4" t="n">
+        <v>380000000</v>
+      </c>
+      <c r="Q4" t="n">
+        <v>95700000</v>
+      </c>
+      <c r="R4" t="n">
+        <v>220500000</v>
+      </c>
+      <c r="S4" t="b">
+        <v>0</v>
+      </c>
+      <c r="T4" t="inlineStr"/>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>동의 거부 - 감정평가 재요청</t>
+        </is>
       </c>
     </row>
     <row r="5">
@@ -526,23 +766,78 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>서울 영등포구 도림동 240-1</t>
+          <t>최정비</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>1971-02-14</t>
-        </is>
-      </c>
-      <c r="D5" t="b">
-        <v>1</v>
-      </c>
-      <c r="E5" t="n">
-        <v>198000000</v>
-      </c>
-      <c r="F5" t="b">
-        <v>1</v>
-      </c>
+          <t>010-1003-5003</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>1970-04-01</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>서울 영등포구 도림동 239-18</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>서울 영등포구 도림동 239-18</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>토지+건물</t>
+        </is>
+      </c>
+      <c r="H5" t="n">
+        <v>55</v>
+      </c>
+      <c r="I5" t="n">
+        <v>99.2</v>
+      </c>
+      <c r="J5" t="b">
+        <v>0</v>
+      </c>
+      <c r="K5" t="n">
+        <v>190000000</v>
+      </c>
+      <c r="L5" t="n">
+        <v>110</v>
+      </c>
+      <c r="M5" t="n">
+        <v>209000000</v>
+      </c>
+      <c r="N5" t="b">
+        <v>1</v>
+      </c>
+      <c r="O5" t="inlineStr">
+        <is>
+          <t>84B</t>
+        </is>
+      </c>
+      <c r="P5" t="n">
+        <v>620000000</v>
+      </c>
+      <c r="Q5" t="n">
+        <v>125400000</v>
+      </c>
+      <c r="R5" t="n">
+        <v>411000000</v>
+      </c>
+      <c r="S5" t="b">
+        <v>1</v>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>2024-03-28</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -550,23 +845,78 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>서울 영등포구 도림동 240-3</t>
+          <t>정조합</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>1965-09-30</t>
-        </is>
-      </c>
-      <c r="D6" t="b">
-        <v>1</v>
-      </c>
-      <c r="E6" t="n">
-        <v>175000000</v>
-      </c>
-      <c r="F6" t="b">
-        <v>0</v>
-      </c>
+          <t>010-1004-5004</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>1983-09-14</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>서울 영등포구 도림동 239-20</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>서울 영등포구 도림동 239-20</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>건물만</t>
+        </is>
+      </c>
+      <c r="H6" t="n">
+        <v>0</v>
+      </c>
+      <c r="I6" t="n">
+        <v>55</v>
+      </c>
+      <c r="J6" t="b">
+        <v>0</v>
+      </c>
+      <c r="K6" t="n">
+        <v>95000000</v>
+      </c>
+      <c r="L6" t="n">
+        <v>110</v>
+      </c>
+      <c r="M6" t="n">
+        <v>104500000</v>
+      </c>
+      <c r="N6" t="b">
+        <v>0</v>
+      </c>
+      <c r="O6" t="inlineStr">
+        <is>
+          <t>미신청</t>
+        </is>
+      </c>
+      <c r="P6" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q6" t="n">
+        <v>62700000</v>
+      </c>
+      <c r="R6" t="n">
+        <v>0</v>
+      </c>
+      <c r="S6" t="b">
+        <v>1</v>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>2024-05-10</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -574,23 +924,78 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>서울 영등포구 도림동 241-2</t>
+          <t>한건물</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>1953-06-18</t>
-        </is>
-      </c>
-      <c r="D7" t="b">
-        <v>1</v>
-      </c>
-      <c r="E7" t="n">
-        <v>210000000</v>
-      </c>
-      <c r="F7" t="b">
-        <v>1</v>
-      </c>
+          <t>010-1005-5005</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>1951-01-29</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>서울 영등포구 도림동 239-22</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>서울 영등포구 도림동 239-22</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>토지+건물</t>
+        </is>
+      </c>
+      <c r="H7" t="n">
+        <v>78.3</v>
+      </c>
+      <c r="I7" t="n">
+        <v>143</v>
+      </c>
+      <c r="J7" t="b">
+        <v>0</v>
+      </c>
+      <c r="K7" t="n">
+        <v>260000000</v>
+      </c>
+      <c r="L7" t="n">
+        <v>110</v>
+      </c>
+      <c r="M7" t="n">
+        <v>286000000</v>
+      </c>
+      <c r="N7" t="b">
+        <v>1</v>
+      </c>
+      <c r="O7" t="inlineStr">
+        <is>
+          <t>120A</t>
+        </is>
+      </c>
+      <c r="P7" t="n">
+        <v>760000000</v>
+      </c>
+      <c r="Q7" t="n">
+        <v>171600000</v>
+      </c>
+      <c r="R7" t="n">
+        <v>474000000</v>
+      </c>
+      <c r="S7" t="b">
+        <v>1</v>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>2024-04-15</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -598,22 +1003,77 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>서울 영등포구 도림동 241-5</t>
+          <t>오재개</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>1978-12-25</t>
-        </is>
-      </c>
-      <c r="D8" t="b">
-        <v>0</v>
-      </c>
-      <c r="E8" t="n">
-        <v>130000000</v>
-      </c>
-      <c r="F8" t="b">
-        <v>0</v>
+          <t>010-1006-5006</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>1965-06-17</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>서울 영등포구 도림동 239-24</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>서울 영등포구 도림동 239-24</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>토지+건물</t>
+        </is>
+      </c>
+      <c r="H8" t="n">
+        <v>42.1</v>
+      </c>
+      <c r="I8" t="n">
+        <v>76.40000000000001</v>
+      </c>
+      <c r="J8" t="b">
+        <v>0</v>
+      </c>
+      <c r="K8" t="n">
+        <v>165000000</v>
+      </c>
+      <c r="L8" t="n">
+        <v>110</v>
+      </c>
+      <c r="M8" t="n">
+        <v>181500000</v>
+      </c>
+      <c r="N8" t="b">
+        <v>1</v>
+      </c>
+      <c r="O8" t="inlineStr">
+        <is>
+          <t>84A</t>
+        </is>
+      </c>
+      <c r="P8" t="n">
+        <v>490000000</v>
+      </c>
+      <c r="Q8" t="n">
+        <v>108900000</v>
+      </c>
+      <c r="R8" t="n">
+        <v>308500000</v>
+      </c>
+      <c r="S8" t="b">
+        <v>0</v>
+      </c>
+      <c r="T8" t="inlineStr"/>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>이주 준비 중 연락 불가</t>
+        </is>
       </c>
     </row>
     <row r="9">
@@ -622,22 +1082,81 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>서울 영등포구 도림동 242-1</t>
+          <t>임토지</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>1960-04-11</t>
-        </is>
-      </c>
-      <c r="D9" t="b">
-        <v>1</v>
-      </c>
-      <c r="E9" t="n">
-        <v>195000000</v>
-      </c>
-      <c r="F9" t="b">
-        <v>1</v>
+          <t>010-1007-5007</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>1979-12-03</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>서울 영등포구 도림동 239-26</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>서울 영등포구 도림동 239-26</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>무허가건물</t>
+        </is>
+      </c>
+      <c r="H9" t="n">
+        <v>0</v>
+      </c>
+      <c r="I9" t="n">
+        <v>40</v>
+      </c>
+      <c r="J9" t="b">
+        <v>1</v>
+      </c>
+      <c r="K9" t="n">
+        <v>75000000</v>
+      </c>
+      <c r="L9" t="n">
+        <v>110</v>
+      </c>
+      <c r="M9" t="n">
+        <v>82500000</v>
+      </c>
+      <c r="N9" t="b">
+        <v>0</v>
+      </c>
+      <c r="O9" t="inlineStr">
+        <is>
+          <t>59A</t>
+        </is>
+      </c>
+      <c r="P9" t="n">
+        <v>350000000</v>
+      </c>
+      <c r="Q9" t="n">
+        <v>49500000</v>
+      </c>
+      <c r="R9" t="n">
+        <v>267500000</v>
+      </c>
+      <c r="S9" t="b">
+        <v>1</v>
+      </c>
+      <c r="T9" t="inlineStr">
+        <is>
+          <t>2024-03-22</t>
+        </is>
+      </c>
+      <c r="U9" t="inlineStr">
+        <is>
+          <t>장기 부재 중</t>
+        </is>
       </c>
     </row>
     <row r="10">
@@ -646,23 +1165,78 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>서울 영등포구 도림동 242-3</t>
+          <t>신권리</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>1967-08-07</t>
-        </is>
-      </c>
-      <c r="D10" t="b">
-        <v>1</v>
-      </c>
-      <c r="E10" t="n">
-        <v>168000000</v>
-      </c>
-      <c r="F10" t="b">
-        <v>1</v>
-      </c>
+          <t>010-1008-5008</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>1958-08-25</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>서울 영등포구 도림동 239-28</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>서울 영등포구 도림동 239-28</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>토지+건물</t>
+        </is>
+      </c>
+      <c r="H10" t="n">
+        <v>60</v>
+      </c>
+      <c r="I10" t="n">
+        <v>108.7</v>
+      </c>
+      <c r="J10" t="b">
+        <v>0</v>
+      </c>
+      <c r="K10" t="n">
+        <v>205000000</v>
+      </c>
+      <c r="L10" t="n">
+        <v>110</v>
+      </c>
+      <c r="M10" t="n">
+        <v>225500000</v>
+      </c>
+      <c r="N10" t="b">
+        <v>1</v>
+      </c>
+      <c r="O10" t="inlineStr">
+        <is>
+          <t>84B</t>
+        </is>
+      </c>
+      <c r="P10" t="n">
+        <v>650000000</v>
+      </c>
+      <c r="Q10" t="n">
+        <v>135300000</v>
+      </c>
+      <c r="R10" t="n">
+        <v>424500000</v>
+      </c>
+      <c r="S10" t="b">
+        <v>1</v>
+      </c>
+      <c r="T10" t="inlineStr">
+        <is>
+          <t>2024-04-18</t>
+        </is>
+      </c>
+      <c r="U10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -670,23 +1244,78 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>서울 영등포구 도림동 243-2</t>
+          <t>황분양</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>1982-01-19</t>
-        </is>
-      </c>
-      <c r="D11" t="b">
-        <v>1</v>
-      </c>
-      <c r="E11" t="n">
-        <v>205000000</v>
-      </c>
-      <c r="F11" t="b">
-        <v>0</v>
-      </c>
+          <t>010-1009-5009</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>1972-02-11</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>서울 영등포구 도림동 239-30</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>서울 영등포구 도림동 239-30</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>토지+건물</t>
+        </is>
+      </c>
+      <c r="H11" t="n">
+        <v>48.7</v>
+      </c>
+      <c r="I11" t="n">
+        <v>88.09999999999999</v>
+      </c>
+      <c r="J11" t="b">
+        <v>0</v>
+      </c>
+      <c r="K11" t="n">
+        <v>175000000</v>
+      </c>
+      <c r="L11" t="n">
+        <v>110</v>
+      </c>
+      <c r="M11" t="n">
+        <v>192500000</v>
+      </c>
+      <c r="N11" t="b">
+        <v>1</v>
+      </c>
+      <c r="O11" t="inlineStr">
+        <is>
+          <t>84A</t>
+        </is>
+      </c>
+      <c r="P11" t="n">
+        <v>560000000</v>
+      </c>
+      <c r="Q11" t="n">
+        <v>115500000</v>
+      </c>
+      <c r="R11" t="n">
+        <v>367500000</v>
+      </c>
+      <c r="S11" t="b">
+        <v>1</v>
+      </c>
+      <c r="T11" t="inlineStr">
+        <is>
+          <t>2024-05-02</t>
+        </is>
+      </c>
+      <c r="U11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -694,22 +1323,77 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>서울 영등포구 도림동 243-4</t>
+          <t>류이주</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>1950-10-05</t>
-        </is>
-      </c>
-      <c r="D12" t="b">
-        <v>0</v>
-      </c>
-      <c r="E12" t="n">
-        <v>155000000</v>
-      </c>
-      <c r="F12" t="b">
-        <v>1</v>
+          <t>010-1010-5010</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>1945-10-20</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>서울 영등포구 도림동 240-1</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>서울 영등포구 도림동 240-1</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>토지+건물</t>
+        </is>
+      </c>
+      <c r="H12" t="n">
+        <v>52.4</v>
+      </c>
+      <c r="I12" t="n">
+        <v>95.5</v>
+      </c>
+      <c r="J12" t="b">
+        <v>0</v>
+      </c>
+      <c r="K12" t="n">
+        <v>195000000</v>
+      </c>
+      <c r="L12" t="n">
+        <v>110</v>
+      </c>
+      <c r="M12" t="n">
+        <v>214500000</v>
+      </c>
+      <c r="N12" t="b">
+        <v>1</v>
+      </c>
+      <c r="O12" t="inlineStr">
+        <is>
+          <t>84A</t>
+        </is>
+      </c>
+      <c r="P12" t="n">
+        <v>580000000</v>
+      </c>
+      <c r="Q12" t="n">
+        <v>128700000</v>
+      </c>
+      <c r="R12" t="n">
+        <v>365500000</v>
+      </c>
+      <c r="S12" t="b">
+        <v>0</v>
+      </c>
+      <c r="T12" t="inlineStr"/>
+      <c r="U12" t="inlineStr">
+        <is>
+          <t>세입자 명도 분쟁 중</t>
+        </is>
       </c>
     </row>
     <row r="13">
@@ -718,23 +1402,78 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>서울 영등포구 도림동 244-1</t>
+          <t>문청산</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>1974-03-28</t>
-        </is>
-      </c>
-      <c r="D13" t="b">
-        <v>1</v>
-      </c>
-      <c r="E13" t="n">
-        <v>182000000</v>
-      </c>
-      <c r="F13" t="b">
-        <v>0</v>
-      </c>
+          <t>010-1011-5011</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>1987-05-06</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>서울 영등포구 도림동 240-3</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>서울 영등포구 도림동 240-3</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>토지만</t>
+        </is>
+      </c>
+      <c r="H13" t="n">
+        <v>33</v>
+      </c>
+      <c r="I13" t="n">
+        <v>0</v>
+      </c>
+      <c r="J13" t="b">
+        <v>0</v>
+      </c>
+      <c r="K13" t="n">
+        <v>110000000</v>
+      </c>
+      <c r="L13" t="n">
+        <v>110</v>
+      </c>
+      <c r="M13" t="n">
+        <v>121000000</v>
+      </c>
+      <c r="N13" t="b">
+        <v>0</v>
+      </c>
+      <c r="O13" t="inlineStr">
+        <is>
+          <t>미신청</t>
+        </is>
+      </c>
+      <c r="P13" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q13" t="n">
+        <v>72600000</v>
+      </c>
+      <c r="R13" t="n">
+        <v>0</v>
+      </c>
+      <c r="S13" t="b">
+        <v>1</v>
+      </c>
+      <c r="T13" t="inlineStr">
+        <is>
+          <t>2024-03-30</t>
+        </is>
+      </c>
+      <c r="U13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -742,23 +1481,78 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>서울 영등포구 도림동 244-6</t>
+          <t>노비례</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>1958-07-14</t>
-        </is>
-      </c>
-      <c r="D14" t="b">
-        <v>1</v>
-      </c>
-      <c r="E14" t="n">
-        <v>225000000</v>
-      </c>
-      <c r="F14" t="b">
-        <v>1</v>
-      </c>
+          <t>010-1012-5012</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>1953-07-30</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>서울 영등포구 도림동 240-5</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>서울 영등포구 도림동 240-5</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>토지+건물</t>
+        </is>
+      </c>
+      <c r="H14" t="n">
+        <v>70.09999999999999</v>
+      </c>
+      <c r="I14" t="n">
+        <v>127.3</v>
+      </c>
+      <c r="J14" t="b">
+        <v>0</v>
+      </c>
+      <c r="K14" t="n">
+        <v>235000000</v>
+      </c>
+      <c r="L14" t="n">
+        <v>110</v>
+      </c>
+      <c r="M14" t="n">
+        <v>258500000</v>
+      </c>
+      <c r="N14" t="b">
+        <v>1</v>
+      </c>
+      <c r="O14" t="inlineStr">
+        <is>
+          <t>120A</t>
+        </is>
+      </c>
+      <c r="P14" t="n">
+        <v>720000000</v>
+      </c>
+      <c r="Q14" t="n">
+        <v>155100000</v>
+      </c>
+      <c r="R14" t="n">
+        <v>461500000</v>
+      </c>
+      <c r="S14" t="b">
+        <v>1</v>
+      </c>
+      <c r="T14" t="inlineStr">
+        <is>
+          <t>2024-04-08</t>
+        </is>
+      </c>
+      <c r="U14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -766,23 +1560,78 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>서울 영등포구 도림동 245-3</t>
+          <t>배동의</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>1945-12-01</t>
-        </is>
-      </c>
-      <c r="D15" t="b">
-        <v>0</v>
-      </c>
-      <c r="E15" t="n">
-        <v>140000000</v>
-      </c>
-      <c r="F15" t="b">
-        <v>0</v>
-      </c>
+          <t>010-1013-5013</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>1968-03-19</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>서울 영등포구 도림동 240-7</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>서울 영등포구 도림동 240-7</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>토지+건물</t>
+        </is>
+      </c>
+      <c r="H15" t="n">
+        <v>44.5</v>
+      </c>
+      <c r="I15" t="n">
+        <v>79.90000000000001</v>
+      </c>
+      <c r="J15" t="b">
+        <v>0</v>
+      </c>
+      <c r="K15" t="n">
+        <v>160000000</v>
+      </c>
+      <c r="L15" t="n">
+        <v>110</v>
+      </c>
+      <c r="M15" t="n">
+        <v>176000000</v>
+      </c>
+      <c r="N15" t="b">
+        <v>1</v>
+      </c>
+      <c r="O15" t="inlineStr">
+        <is>
+          <t>84A</t>
+        </is>
+      </c>
+      <c r="P15" t="n">
+        <v>500000000</v>
+      </c>
+      <c r="Q15" t="n">
+        <v>105600000</v>
+      </c>
+      <c r="R15" t="n">
+        <v>324000000</v>
+      </c>
+      <c r="S15" t="b">
+        <v>1</v>
+      </c>
+      <c r="T15" t="inlineStr">
+        <is>
+          <t>2024-03-25</t>
+        </is>
+      </c>
+      <c r="U15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -790,22 +1639,77 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>서울 영등포구 도림동 245-7</t>
+          <t>조관리</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>1969-05-22</t>
-        </is>
-      </c>
-      <c r="D16" t="b">
-        <v>1</v>
-      </c>
-      <c r="E16" t="n">
-        <v>190000000</v>
-      </c>
-      <c r="F16" t="b">
-        <v>1</v>
+          <t>010-1014-5014</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>1991-11-27</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>서울 영등포구 도림동 240-9</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>서울 영등포구 도림동 240-9</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>건물만</t>
+        </is>
+      </c>
+      <c r="H16" t="n">
+        <v>0</v>
+      </c>
+      <c r="I16" t="n">
+        <v>48.5</v>
+      </c>
+      <c r="J16" t="b">
+        <v>0</v>
+      </c>
+      <c r="K16" t="n">
+        <v>85000000</v>
+      </c>
+      <c r="L16" t="n">
+        <v>110</v>
+      </c>
+      <c r="M16" t="n">
+        <v>93500000</v>
+      </c>
+      <c r="N16" t="b">
+        <v>1</v>
+      </c>
+      <c r="O16" t="inlineStr">
+        <is>
+          <t>59A</t>
+        </is>
+      </c>
+      <c r="P16" t="n">
+        <v>310000000</v>
+      </c>
+      <c r="Q16" t="n">
+        <v>56100000</v>
+      </c>
+      <c r="R16" t="n">
+        <v>216500000</v>
+      </c>
+      <c r="S16" t="b">
+        <v>0</v>
+      </c>
+      <c r="T16" t="inlineStr"/>
+      <c r="U16" t="inlineStr">
+        <is>
+          <t>건물 철거 협의 필요</t>
+        </is>
       </c>
     </row>
     <row r="17">
@@ -814,23 +1718,78 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>서울 영등포구 도림동 246-1</t>
+          <t>윤처분</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>1973-09-16</t>
-        </is>
-      </c>
-      <c r="D17" t="b">
-        <v>1</v>
-      </c>
-      <c r="E17" t="n">
-        <v>178000000</v>
-      </c>
-      <c r="F17" t="b">
-        <v>1</v>
-      </c>
+          <t>010-1015-5015</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>1960-09-08</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>서울 영등포구 도림동 241-2</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>서울 영등포구 도림동 241-2</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>토지+건물</t>
+        </is>
+      </c>
+      <c r="H17" t="n">
+        <v>65.8</v>
+      </c>
+      <c r="I17" t="n">
+        <v>118.2</v>
+      </c>
+      <c r="J17" t="b">
+        <v>0</v>
+      </c>
+      <c r="K17" t="n">
+        <v>225000000</v>
+      </c>
+      <c r="L17" t="n">
+        <v>110</v>
+      </c>
+      <c r="M17" t="n">
+        <v>247500000</v>
+      </c>
+      <c r="N17" t="b">
+        <v>1</v>
+      </c>
+      <c r="O17" t="inlineStr">
+        <is>
+          <t>84B</t>
+        </is>
+      </c>
+      <c r="P17" t="n">
+        <v>680000000</v>
+      </c>
+      <c r="Q17" t="n">
+        <v>148500000</v>
+      </c>
+      <c r="R17" t="n">
+        <v>432500000</v>
+      </c>
+      <c r="S17" t="b">
+        <v>1</v>
+      </c>
+      <c r="T17" t="inlineStr">
+        <is>
+          <t>2024-04-20</t>
+        </is>
+      </c>
+      <c r="U17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -838,23 +1797,78 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>서울 영등포구 도림동 246-4</t>
+          <t>진착공</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>1956-02-09</t>
-        </is>
-      </c>
-      <c r="D18" t="b">
-        <v>0</v>
-      </c>
-      <c r="E18" t="n">
-        <v>160000000</v>
-      </c>
-      <c r="F18" t="b">
-        <v>0</v>
-      </c>
+          <t>010-1016-5016</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>1975-04-23</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>서울 영등포구 도림동 241-4</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>서울 영등포구 도림동 241-4</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>토지+건물</t>
+        </is>
+      </c>
+      <c r="H18" t="n">
+        <v>39.2</v>
+      </c>
+      <c r="I18" t="n">
+        <v>71.59999999999999</v>
+      </c>
+      <c r="J18" t="b">
+        <v>0</v>
+      </c>
+      <c r="K18" t="n">
+        <v>150000000</v>
+      </c>
+      <c r="L18" t="n">
+        <v>110</v>
+      </c>
+      <c r="M18" t="n">
+        <v>165000000</v>
+      </c>
+      <c r="N18" t="b">
+        <v>1</v>
+      </c>
+      <c r="O18" t="inlineStr">
+        <is>
+          <t>84A</t>
+        </is>
+      </c>
+      <c r="P18" t="n">
+        <v>430000000</v>
+      </c>
+      <c r="Q18" t="n">
+        <v>99000000</v>
+      </c>
+      <c r="R18" t="n">
+        <v>265000000</v>
+      </c>
+      <c r="S18" t="b">
+        <v>1</v>
+      </c>
+      <c r="T18" t="inlineStr">
+        <is>
+          <t>2024-05-15</t>
+        </is>
+      </c>
+      <c r="U18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -862,22 +1876,77 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>서울 영등포구 도림동 247-2</t>
+          <t>엄준공</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>1980-11-30</t>
-        </is>
-      </c>
-      <c r="D19" t="b">
-        <v>1</v>
-      </c>
-      <c r="E19" t="n">
-        <v>215000000</v>
-      </c>
-      <c r="F19" t="b">
-        <v>1</v>
+          <t>010-1017-5017</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>1949-12-15</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>서울 영등포구 도림동 241-6</t>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>서울 영등포구 도림동 241-6</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>토지+건물</t>
+        </is>
+      </c>
+      <c r="H19" t="n">
+        <v>58.6</v>
+      </c>
+      <c r="I19" t="n">
+        <v>105</v>
+      </c>
+      <c r="J19" t="b">
+        <v>0</v>
+      </c>
+      <c r="K19" t="n">
+        <v>200000000</v>
+      </c>
+      <c r="L19" t="n">
+        <v>110</v>
+      </c>
+      <c r="M19" t="n">
+        <v>220000000</v>
+      </c>
+      <c r="N19" t="b">
+        <v>1</v>
+      </c>
+      <c r="O19" t="inlineStr">
+        <is>
+          <t>84A</t>
+        </is>
+      </c>
+      <c r="P19" t="n">
+        <v>590000000</v>
+      </c>
+      <c r="Q19" t="n">
+        <v>132000000</v>
+      </c>
+      <c r="R19" t="n">
+        <v>370000000</v>
+      </c>
+      <c r="S19" t="b">
+        <v>0</v>
+      </c>
+      <c r="T19" t="inlineStr"/>
+      <c r="U19" t="inlineStr">
+        <is>
+          <t>토지 공유지분 확인 필요</t>
+        </is>
       </c>
     </row>
     <row r="20">
@@ -886,23 +1955,78 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>서울 영등포구 도림동 247-8</t>
+          <t>강입주</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>1963-06-25</t>
-        </is>
-      </c>
-      <c r="D20" t="b">
-        <v>1</v>
-      </c>
-      <c r="E20" t="n">
-        <v>172000000</v>
-      </c>
-      <c r="F20" t="b">
-        <v>0</v>
-      </c>
+          <t>010-1018-5018</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>1982-06-02</t>
+        </is>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>서울 영등포구 도림동 241-8</t>
+        </is>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>서울 영등포구 도림동 241-8</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>무허가건물</t>
+        </is>
+      </c>
+      <c r="H20" t="n">
+        <v>0</v>
+      </c>
+      <c r="I20" t="n">
+        <v>35</v>
+      </c>
+      <c r="J20" t="b">
+        <v>1</v>
+      </c>
+      <c r="K20" t="n">
+        <v>65000000</v>
+      </c>
+      <c r="L20" t="n">
+        <v>110</v>
+      </c>
+      <c r="M20" t="n">
+        <v>71500000</v>
+      </c>
+      <c r="N20" t="b">
+        <v>0</v>
+      </c>
+      <c r="O20" t="inlineStr">
+        <is>
+          <t>59A</t>
+        </is>
+      </c>
+      <c r="P20" t="n">
+        <v>340000000</v>
+      </c>
+      <c r="Q20" t="n">
+        <v>42900000</v>
+      </c>
+      <c r="R20" t="n">
+        <v>268500000</v>
+      </c>
+      <c r="S20" t="b">
+        <v>1</v>
+      </c>
+      <c r="T20" t="inlineStr">
+        <is>
+          <t>2024-04-01</t>
+        </is>
+      </c>
+      <c r="U20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -910,23 +2034,78 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>서울 영등포구 도림동 248-1</t>
+          <t>유청산</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>1970-04-03</t>
-        </is>
-      </c>
-      <c r="D21" t="b">
-        <v>1</v>
-      </c>
-      <c r="E21" t="n">
-        <v>200000000</v>
-      </c>
-      <c r="F21" t="b">
-        <v>1</v>
-      </c>
+          <t>010-1019-5019</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>1964-01-18</t>
+        </is>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>서울 영등포구 도림동 241-10</t>
+        </is>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>서울 영등포구 도림동 241-10</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>토지+건물</t>
+        </is>
+      </c>
+      <c r="H21" t="n">
+        <v>80</v>
+      </c>
+      <c r="I21" t="n">
+        <v>147.6</v>
+      </c>
+      <c r="J21" t="b">
+        <v>0</v>
+      </c>
+      <c r="K21" t="n">
+        <v>280000000</v>
+      </c>
+      <c r="L21" t="n">
+        <v>110</v>
+      </c>
+      <c r="M21" t="n">
+        <v>308000000</v>
+      </c>
+      <c r="N21" t="b">
+        <v>1</v>
+      </c>
+      <c r="O21" t="inlineStr">
+        <is>
+          <t>84B</t>
+        </is>
+      </c>
+      <c r="P21" t="n">
+        <v>820000000</v>
+      </c>
+      <c r="Q21" t="n">
+        <v>184800000</v>
+      </c>
+      <c r="R21" t="n">
+        <v>512000000</v>
+      </c>
+      <c r="S21" t="b">
+        <v>1</v>
+      </c>
+      <c r="T21" t="inlineStr">
+        <is>
+          <t>2024-03-18</t>
+        </is>
+      </c>
+      <c r="U21" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
